--- a/data/jjj/sites.xlsx
+++ b/data/jjj/sites.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,25 +429,15 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>K2站点（渤海十路边界点位）</t>
+          <t>M1站点（临港西部控制点位）</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>K3站点（汉江道边界点位）</t>
+          <t>M2站点（临港东部控制点位）</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>M1站点（临港西部控制点位）</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>M2站点（临港东部控制点位）</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>M3站点（临港南部控制点位）</t>
         </is>
@@ -463,18 +453,12 @@
         <v>117.71633</v>
       </c>
       <c r="C2" t="n">
-        <v>117.70936</v>
+        <v>117.71387</v>
       </c>
       <c r="D2" t="n">
-        <v>117.70022</v>
+        <v>117.75821</v>
       </c>
       <c r="E2" t="n">
-        <v>117.71387</v>
-      </c>
-      <c r="F2" t="n">
-        <v>117.75821</v>
-      </c>
-      <c r="G2" t="n">
         <v>117.69443</v>
       </c>
     </row>
@@ -488,18 +472,12 @@
         <v>38.93774</v>
       </c>
       <c r="C3" t="n">
-        <v>38.95187</v>
+        <v>38.95623</v>
       </c>
       <c r="D3" t="n">
-        <v>38.92277</v>
+        <v>38.91997</v>
       </c>
       <c r="E3" t="n">
-        <v>38.95623</v>
-      </c>
-      <c r="F3" t="n">
-        <v>38.91997</v>
-      </c>
-      <c r="G3" t="n">
         <v>38.91772</v>
       </c>
     </row>

--- a/data/jjj/sites.xlsx
+++ b/data/jjj/sites.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,20 +424,55 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>H1站点（装备制造区域点位）</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>H2站点（罐区区域点位）</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>H3站点（海河道区域点位）</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>H4站点（粮油区域点位）</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>H5站点（淮河道区域点位）</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>K1站点（园区中心点位）</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>K2站点（渤海十路边界点位）</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>K3站点（汉江道边界点位）</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>M1站点（临港西部控制点位）</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>M2站点（临港东部控制点位）</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>M3站点（临港南部控制点位）</t>
         </is>
@@ -450,15 +485,36 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>117.75404</v>
+      </c>
+      <c r="C2" t="n">
+        <v>117.73766</v>
+      </c>
+      <c r="D2" t="n">
+        <v>117.72237</v>
+      </c>
+      <c r="E2" t="n">
+        <v>117.79346</v>
+      </c>
+      <c r="F2" t="n">
+        <v>117.72382</v>
+      </c>
+      <c r="G2" t="n">
         <v>117.71633</v>
       </c>
-      <c r="C2" t="n">
+      <c r="H2" t="n">
+        <v>117.70936</v>
+      </c>
+      <c r="I2" t="n">
+        <v>117.70022</v>
+      </c>
+      <c r="J2" t="n">
         <v>117.71387</v>
       </c>
-      <c r="D2" t="n">
+      <c r="K2" t="n">
         <v>117.75821</v>
       </c>
-      <c r="E2" t="n">
+      <c r="L2" t="n">
         <v>117.69443</v>
       </c>
     </row>
@@ -469,15 +525,36 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>38.93999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>38.95232</v>
+      </c>
+      <c r="D3" t="n">
+        <v>38.94776</v>
+      </c>
+      <c r="E3" t="n">
+        <v>38.91555</v>
+      </c>
+      <c r="F3" t="n">
+        <v>38.93322</v>
+      </c>
+      <c r="G3" t="n">
         <v>38.93774</v>
       </c>
-      <c r="C3" t="n">
+      <c r="H3" t="n">
+        <v>38.95187</v>
+      </c>
+      <c r="I3" t="n">
+        <v>38.92277</v>
+      </c>
+      <c r="J3" t="n">
         <v>38.95623</v>
       </c>
-      <c r="D3" t="n">
+      <c r="K3" t="n">
         <v>38.91997</v>
       </c>
-      <c r="E3" t="n">
+      <c r="L3" t="n">
         <v>38.91772</v>
       </c>
     </row>

--- a/data/jjj/sites.xlsx
+++ b/data/jjj/sites.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,55 +424,20 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>H1站点（装备制造区域点位）</t>
+          <t>K1站点（园区中心点位）</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>H2站点（罐区区域点位）</t>
+          <t>M1站点（临港西部控制点位）</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>H3站点（海河道区域点位）</t>
+          <t>M2站点（临港东部控制点位）</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>H4站点（粮油区域点位）</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>H5站点（淮河道区域点位）</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>K1站点（园区中心点位）</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>K2站点（渤海十路边界点位）</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>K3站点（汉江道边界点位）</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>M1站点（临港西部控制点位）</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>M2站点（临港东部控制点位）</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
         <is>
           <t>M3站点（临港南部控制点位）</t>
         </is>
@@ -485,36 +450,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>117.75404</v>
+        <v>117.71633</v>
       </c>
       <c r="C2" t="n">
-        <v>117.73766</v>
+        <v>117.71387</v>
       </c>
       <c r="D2" t="n">
-        <v>117.72237</v>
+        <v>117.75821</v>
       </c>
       <c r="E2" t="n">
-        <v>117.79346</v>
-      </c>
-      <c r="F2" t="n">
-        <v>117.72382</v>
-      </c>
-      <c r="G2" t="n">
-        <v>117.71633</v>
-      </c>
-      <c r="H2" t="n">
-        <v>117.70936</v>
-      </c>
-      <c r="I2" t="n">
-        <v>117.70022</v>
-      </c>
-      <c r="J2" t="n">
-        <v>117.71387</v>
-      </c>
-      <c r="K2" t="n">
-        <v>117.75821</v>
-      </c>
-      <c r="L2" t="n">
         <v>117.69443</v>
       </c>
     </row>
@@ -525,36 +469,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.93999</v>
+        <v>38.93774</v>
       </c>
       <c r="C3" t="n">
-        <v>38.95232</v>
+        <v>38.95623</v>
       </c>
       <c r="D3" t="n">
-        <v>38.94776</v>
+        <v>38.91997</v>
       </c>
       <c r="E3" t="n">
-        <v>38.91555</v>
-      </c>
-      <c r="F3" t="n">
-        <v>38.93322</v>
-      </c>
-      <c r="G3" t="n">
-        <v>38.93774</v>
-      </c>
-      <c r="H3" t="n">
-        <v>38.95187</v>
-      </c>
-      <c r="I3" t="n">
-        <v>38.92277</v>
-      </c>
-      <c r="J3" t="n">
-        <v>38.95623</v>
-      </c>
-      <c r="K3" t="n">
-        <v>38.91997</v>
-      </c>
-      <c r="L3" t="n">
         <v>38.91772</v>
       </c>
     </row>

--- a/data/jjj/sites.xlsx
+++ b/data/jjj/sites.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,22 +424,62 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>H4站点（粮油区域点位）</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>H5站点（淮河道区域点位）</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>K1站点（园区中心点位）</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>K2站点（渤海十路边界点位）</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>K3站点（汉江道边界点位）</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>M1站点（临港西部控制点位）</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>M2站点（临港东部控制点位）</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>M3站点（临港南部控制点位）</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Z1站点（渤海十路点位）</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Z2站点（辽河道点位）</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Z3站点（渤海十六路点位）</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Z4站点（渤海十八路点位）</t>
         </is>
       </c>
     </row>
@@ -450,16 +490,40 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>117.79346</v>
+      </c>
+      <c r="C2" t="n">
+        <v>117.72382</v>
+      </c>
+      <c r="D2" t="n">
         <v>117.71633</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
+        <v>117.70936</v>
+      </c>
+      <c r="F2" t="n">
+        <v>117.70022</v>
+      </c>
+      <c r="G2" t="n">
         <v>117.71387</v>
       </c>
-      <c r="D2" t="n">
+      <c r="H2" t="n">
         <v>117.75821</v>
       </c>
-      <c r="E2" t="n">
+      <c r="I2" t="n">
         <v>117.69443</v>
+      </c>
+      <c r="J2" t="n">
+        <v>117.70767</v>
+      </c>
+      <c r="K2" t="n">
+        <v>117.71925</v>
+      </c>
+      <c r="L2" t="n">
+        <v>117.732724</v>
+      </c>
+      <c r="M2" t="n">
+        <v>117.72658</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +533,40 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>38.91555</v>
+      </c>
+      <c r="C3" t="n">
+        <v>38.93322</v>
+      </c>
+      <c r="D3" t="n">
         <v>38.93774</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
+        <v>38.95187</v>
+      </c>
+      <c r="F3" t="n">
+        <v>38.92277</v>
+      </c>
+      <c r="G3" t="n">
         <v>38.95623</v>
       </c>
-      <c r="D3" t="n">
+      <c r="H3" t="n">
         <v>38.91997</v>
       </c>
-      <c r="E3" t="n">
+      <c r="I3" t="n">
         <v>38.91772</v>
+      </c>
+      <c r="J3" t="n">
+        <v>38.93918</v>
+      </c>
+      <c r="K3" t="n">
+        <v>38.9569</v>
+      </c>
+      <c r="L3" t="n">
+        <v>38.942783</v>
+      </c>
+      <c r="M3" t="n">
+        <v>38.92866</v>
       </c>
     </row>
   </sheetData>
